--- a/data/trans_bre/P16A04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,09</t>
+          <t>0,78; 5,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,38</t>
+          <t>-2,69; 5,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,41</t>
+          <t>-0,68; 4,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,99</t>
+          <t>0,63; 4,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 189,16</t>
+          <t>-36,12; 154,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 943,21</t>
+          <t>-42,97; 927,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,6</t>
+          <t>0,25; 3,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,18</t>
+          <t>-2,6; 1,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,07</t>
+          <t>-2,25; 1,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,14</t>
+          <t>-1,15; 2,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 652,39</t>
+          <t>-1,72; 769,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,0; 132,56</t>
+          <t>-79,55; 149,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,96; 154,94</t>
+          <t>-75,85; 130,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 353,31</t>
+          <t>-45,31; 338,79</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,75</t>
+          <t>-0,32; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,18</t>
+          <t>-0,75; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,61</t>
+          <t>-2,65; 1,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,98</t>
+          <t>-2,98; 2,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 630,44</t>
+          <t>-52,72; 627,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 140,91</t>
+          <t>-77,11; 147,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,94; 89,16</t>
+          <t>-47,99; 84,89</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,69</t>
+          <t>-0,8; 3,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,11</t>
+          <t>-3,14; 2,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,73</t>
+          <t>-2,14; 2,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,5</t>
+          <t>-2,08; 1,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 352,91</t>
+          <t>-37,44; 411,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,97; 118,97</t>
+          <t>-67,28; 134,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,91; 234,89</t>
+          <t>-62,77; 193,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,53; 1748,06</t>
+          <t>-96,67; 1081,62</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,07</t>
+          <t>0,11; 4,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 4,57</t>
+          <t>-4,45; 4,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 4,47</t>
+          <t>-1,46; 4,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,16</t>
+          <t>0,01; 3,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-65,6; 197,82</t>
+          <t>-62,19; 210,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-79,74; 754,79</t>
+          <t>-71,47; 1166,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-40,66; —</t>
+          <t>-33,51; —</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,8</t>
+          <t>-1,29; 3,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,3</t>
+          <t>-2,02; 2,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,34</t>
+          <t>-2,08; 1,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,44</t>
+          <t>-3,17; 3,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 759,65</t>
+          <t>-71,73; 770,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 119,77</t>
+          <t>-49,13; 102,49</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,26</t>
+          <t>-2,44; 0,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,91</t>
+          <t>-1,02; 1,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,52</t>
+          <t>-2,69; 1,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,03</t>
+          <t>-3,47; 3,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 37,87</t>
+          <t>-84,62; 58,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 251,78</t>
+          <t>-54,36; 208,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 67,76</t>
+          <t>-60,53; 84,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,97; 76,75</t>
+          <t>-55,36; 88,33</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,36</t>
+          <t>-3,27; 0,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,2</t>
+          <t>-2,54; 1,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,44</t>
+          <t>-0,29; 2,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,71</t>
+          <t>-0,14; 3,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,3; 17,01</t>
+          <t>-68,29; 21,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,99; 49,99</t>
+          <t>-52,41; 37,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 327,38</t>
+          <t>-22,77; 361,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 1668,83</t>
+          <t>-49,81; 1265,57</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,2</t>
+          <t>-0,25; 1,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,88</t>
+          <t>-0,91; 0,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,98</t>
+          <t>-0,45; 1,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,81</t>
+          <t>0,11; 1,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 80,16</t>
+          <t>-12,04; 76,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 37,74</t>
+          <t>-27,9; 35,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 55,63</t>
+          <t>-19,66; 59,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 106,98</t>
+          <t>4,36; 107,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>724,26%</t>
+          <t>985,96%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,22</t>
+          <t>0,78; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 5,82</t>
+          <t>-2,87; 5,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,44</t>
+          <t>-0,77; 4,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,89</t>
+          <t>0,96; 4,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 154,57</t>
+          <t>-39,23; 176,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 927,6</t>
+          <t>-45,79; 751,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,89</t>
+          <t>0,14; 3,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,18</t>
+          <t>-2,45; 1,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,01</t>
+          <t>-2,33; 0,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,01</t>
+          <t>-1,33; 1,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 769,58</t>
+          <t>-6,35; 642,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,55; 149,65</t>
+          <t>-81,37; 134,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,85; 130,74</t>
+          <t>-79,71; 98,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,31; 338,79</t>
+          <t>-53,24; 253,61</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,77</t>
+          <t>-0,34; 2,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,2</t>
+          <t>-0,77; 3,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,73</t>
+          <t>-2,41; 1,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,69</t>
+          <t>-2,47; 3,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,72; 627,44</t>
+          <t>-53,75; 732,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 147,27</t>
+          <t>-71,03; 198,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,99; 84,89</t>
+          <t>-40,8; 102,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,54</t>
+          <t>-0,73; 3,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,53</t>
+          <t>-3,26; 2,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 2,57</t>
+          <t>-2,36; 2,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,4</t>
+          <t>-1,95; 2,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,44; 411,98</t>
+          <t>-37,96; 372,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,28; 134,04</t>
+          <t>-69,24; 159,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,77; 193,65</t>
+          <t>-66,5; 187,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-96,67; 1081,62</t>
+          <t>-79,48; 1086,29</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>203,1%</t>
+          <t>208,97%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,79</t>
+          <t>0,45; 5,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 4,55</t>
+          <t>-4,89; 3,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,61</t>
+          <t>-1,7; 4,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,19</t>
+          <t>-0,2; 2,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-62,19; 210,25</t>
+          <t>-64,76; 155,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-71,47; 1166,23</t>
+          <t>-84,03; 1014,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,51; —</t>
+          <t>-53,99; —</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,87</t>
+          <t>-1,01; 3,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,27</t>
+          <t>-2,07; 2,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,34</t>
+          <t>-2,15; 1,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,0</t>
+          <t>-2,7; 3,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,73; 770,14</t>
+          <t>-60,79; 832,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 102,49</t>
+          <t>-46,48; 101,76</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,24</t>
+          <t>-2,38; 0,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,84</t>
+          <t>-1,04; 1,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,59</t>
+          <t>-2,54; 1,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 3,2</t>
+          <t>-0,46; 4,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-84,62; 58,36</t>
+          <t>-85,36; 38,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,36; 208,2</t>
+          <t>-58,44; 199,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 84,67</t>
+          <t>-59,07; 74,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 88,33</t>
+          <t>-7,64; 126,2</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>163,26%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,53</t>
+          <t>-3,24; 0,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,28</t>
+          <t>-2,92; 1,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,44</t>
+          <t>-0,32; 2,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,92</t>
+          <t>-1,09; 0,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,29; 21,09</t>
+          <t>-66,91; 16,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 37,41</t>
+          <t>-57,09; 49,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 361,23</t>
+          <t>-22,88; 328,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 1265,57</t>
+          <t>-68,44; 339,68</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,1</t>
+          <t>-0,29; 1,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,86</t>
+          <t>-0,86; 0,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,01</t>
+          <t>-0,47; 0,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,82</t>
+          <t>0,23; 1,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 76,57</t>
+          <t>-14,59; 76,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 35,43</t>
+          <t>-24,93; 39,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 59,52</t>
+          <t>-20,1; 58,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 107,77</t>
+          <t>7,87; 88,51</t>
         </is>
       </c>
     </row>
